--- a/Book 1.xlsx
+++ b/Book 1.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20400" windowHeight="7755" tabRatio="0" firstSheet="5" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20400" windowHeight="7755" tabRatio="520" firstSheet="1" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="CORES PADRÃO" sheetId="1" state="hidden" r:id="rId1"/>
@@ -349,7 +349,7 @@
     <numFmt numFmtId="164" formatCode="000&quot;.&quot;000&quot;.&quot;000&quot;-&quot;00"/>
     <numFmt numFmtId="165" formatCode="00000\-000"/>
     <numFmt numFmtId="166" formatCode="&quot;(&quot;00&quot;)&quot;\ 00000&quot;-&quot;0000"/>
-    <numFmt numFmtId="168" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="167" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
   <fonts count="19">
     <font>
@@ -820,27 +820,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="3"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="168" fontId="17" fillId="8" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -880,7 +865,7 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="8" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="167" fontId="11" fillId="8" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
@@ -896,16 +881,31 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="18" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="18" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="3"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="8" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Entrada" xfId="2" builtinId="20"/>
@@ -931,7 +931,20 @@
         <name val="Calibri"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="168" formatCode="&quot;R$&quot;\ #,##0.00"/>
+      <numFmt numFmtId="167" formatCode="&quot;R$&quot;\ #,##0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="&quot;R$&quot;\ #,##0.00"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <protection locked="0" hidden="0"/>
     </dxf>
@@ -948,17 +961,36 @@
       <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="168" formatCode="&quot;R$&quot;\ #,##0.00"/>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF2A3723"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <protection locked="0" hidden="0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -997,252 +1029,6 @@
         </horizontal>
       </border>
       <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF0C0A08"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </horizontal>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF0C0A08"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </horizontal>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF0C0A08"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="2" tint="-0.249977111117893"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color theme="2" tint="-0.249977111117893"/>
-        </top>
-        <bottom style="thin">
-          <color theme="2" tint="-0.249977111117893"/>
-        </bottom>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF2A3723"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF7F7F7F"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FF7F7F7F"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF7F7F7F"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </right>
-        <top style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </left>
-        <right style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </right>
-        <top/>
-        <bottom style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </left>
-        <right style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </horizontal>
-      </border>
     </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0" outline="0">
@@ -1352,6 +1138,58 @@
     </dxf>
     <dxf>
       <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF0C0A08"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </horizontal>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF7F7F7F"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FF7F7F7F"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF7F7F7F"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -1404,6 +1242,83 @@
       </font>
     </dxf>
     <dxf>
+      <border>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top/>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF0C0A08"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </horizontal>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF7F7F7F"/>
@@ -1416,6 +1331,59 @@
           <color rgb="FF7F7F7F"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
     </dxf>
     <dxf>
       <border>
@@ -1455,6 +1423,38 @@
           <color theme="2" tint="-9.9948118533890809E-2"/>
         </horizontal>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF0C0A08"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="2" tint="-0.249977111117893"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="2" tint="-0.249977111117893"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-0.249977111117893"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0" outline="0">
@@ -1786,8 +1786,8 @@
         </c:dLbls>
         <c:gapWidth val="267"/>
         <c:overlap val="-43"/>
-        <c:axId val="406493616"/>
-        <c:axId val="406505040"/>
+        <c:axId val="-879980336"/>
+        <c:axId val="-685908448"/>
         <c:extLst>
           <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
             <c15:filteredBarSeries>
@@ -1900,7 +1900,7 @@
         </c:extLst>
       </c:barChart>
       <c:catAx>
-        <c:axId val="406493616"/>
+        <c:axId val="-879980336"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1954,7 +1954,7 @@
             <a:endParaRPr lang="pt-BR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="406505040"/>
+        <c:crossAx val="-685908448"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1962,7 +1962,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="406505040"/>
+        <c:axId val="-685908448"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1972,7 +1972,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="406493616"/>
+        <c:crossAx val="-879980336"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2530,11 +2530,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="128"/>
-        <c:axId val="486021504"/>
-        <c:axId val="486025856"/>
+        <c:axId val="-685913344"/>
+        <c:axId val="-685912800"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="486021504"/>
+        <c:axId val="-685913344"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2574,7 +2574,7 @@
             <a:endParaRPr lang="pt-BR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="486025856"/>
+        <c:crossAx val="-685912800"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2582,7 +2582,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="486025856"/>
+        <c:axId val="-685912800"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2601,7 +2601,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="486021504"/>
+        <c:crossAx val="-685913344"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4370,10 +4370,10 @@
         <xdr:cNvPr id="8" name="Imagem 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{DD5544AB-9FFC-142D-6E26-CD35F994ABBA}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD5544AB-9FFC-142D-6E26-CD35F994ABBA}"/>
             </a:ext>
             <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" pred="{07E9C1F5-6973-C4E7-F22A-8FC08C2AB984}"/>
+              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{07E9C1F5-6973-C4E7-F22A-8FC08C2AB984}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4417,10 +4417,10 @@
         <xdr:cNvPr id="7" name="Retângulo 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{07E9C1F5-6973-C4E7-F22A-8FC08C2AB984}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07E9C1F5-6973-C4E7-F22A-8FC08C2AB984}"/>
             </a:ext>
             <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" pred="{DD5544AB-9FFC-142D-6E26-CD35F994ABBA}"/>
+              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{DD5544AB-9FFC-142D-6E26-CD35F994ABBA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4495,10 +4495,10 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6715A6CC-3A6A-A1DB-3E76-6B956BB6C7D0}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6715A6CC-3A6A-A1DB-3E76-6B956BB6C7D0}"/>
             </a:ext>
             <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" pred="{07E9C1F5-6973-C4E7-F22A-8FC08C2AB984}"/>
+              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{07E9C1F5-6973-C4E7-F22A-8FC08C2AB984}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4576,10 +4576,10 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{67A41256-9299-4DF9-9708-1493DA40FCED}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67A41256-9299-4DF9-9708-1493DA40FCED}"/>
             </a:ext>
             <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" pred="{6715A6CC-3A6A-A1DB-3E76-6B956BB6C7D0}"/>
+              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{6715A6CC-3A6A-A1DB-3E76-6B956BB6C7D0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4749,10 +4749,10 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8AA0A94E-7223-4757-BA7D-46C6CDA719B2}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8AA0A94E-7223-4757-BA7D-46C6CDA719B2}"/>
             </a:ext>
             <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" pred="{67A41256-9299-4DF9-9708-1493DA40FCED}"/>
+              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{67A41256-9299-4DF9-9708-1493DA40FCED}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5086,10 +5086,10 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8AA0A94E-7223-4757-BA7D-46C6CDA719B2}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8AA0A94E-7223-4757-BA7D-46C6CDA719B2}"/>
             </a:ext>
             <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" pred="{67A41256-9299-4DF9-9708-1493DA40FCED}"/>
+              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{67A41256-9299-4DF9-9708-1493DA40FCED}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5265,10 +5265,10 @@
         <xdr:cNvPr id="2" name="Imagem 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{DD5544AB-9FFC-142D-6E26-CD35F994ABBA}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD5544AB-9FFC-142D-6E26-CD35F994ABBA}"/>
             </a:ext>
             <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" pred="{07E9C1F5-6973-C4E7-F22A-8FC08C2AB984}"/>
+              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{07E9C1F5-6973-C4E7-F22A-8FC08C2AB984}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5312,10 +5312,10 @@
         <xdr:cNvPr id="3" name="Retângulo 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{07E9C1F5-6973-C4E7-F22A-8FC08C2AB984}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07E9C1F5-6973-C4E7-F22A-8FC08C2AB984}"/>
             </a:ext>
             <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" pred="{DD5544AB-9FFC-142D-6E26-CD35F994ABBA}"/>
+              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{DD5544AB-9FFC-142D-6E26-CD35F994ABBA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5390,10 +5390,10 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6715A6CC-3A6A-A1DB-3E76-6B956BB6C7D0}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6715A6CC-3A6A-A1DB-3E76-6B956BB6C7D0}"/>
             </a:ext>
             <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" pred="{07E9C1F5-6973-C4E7-F22A-8FC08C2AB984}"/>
+              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{07E9C1F5-6973-C4E7-F22A-8FC08C2AB984}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5469,10 +5469,10 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{67A41256-9299-4DF9-9708-1493DA40FCED}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67A41256-9299-4DF9-9708-1493DA40FCED}"/>
             </a:ext>
             <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" pred="{6715A6CC-3A6A-A1DB-3E76-6B956BB6C7D0}"/>
+              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{6715A6CC-3A6A-A1DB-3E76-6B956BB6C7D0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5644,10 +5644,10 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8AA0A94E-7223-4757-BA7D-46C6CDA719B2}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8AA0A94E-7223-4757-BA7D-46C6CDA719B2}"/>
             </a:ext>
             <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" pred="{67A41256-9299-4DF9-9708-1493DA40FCED}"/>
+              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{67A41256-9299-4DF9-9708-1493DA40FCED}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6052,10 +6052,10 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8AA0A94E-7223-4757-BA7D-46C6CDA719B2}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8AA0A94E-7223-4757-BA7D-46C6CDA719B2}"/>
             </a:ext>
             <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" pred="{67A41256-9299-4DF9-9708-1493DA40FCED}"/>
+              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{67A41256-9299-4DF9-9708-1493DA40FCED}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6231,10 +6231,10 @@
         <xdr:cNvPr id="2" name="Imagem 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{DD5544AB-9FFC-142D-6E26-CD35F994ABBA}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD5544AB-9FFC-142D-6E26-CD35F994ABBA}"/>
             </a:ext>
             <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" pred="{07E9C1F5-6973-C4E7-F22A-8FC08C2AB984}"/>
+              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{07E9C1F5-6973-C4E7-F22A-8FC08C2AB984}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6278,10 +6278,10 @@
         <xdr:cNvPr id="3" name="Retângulo 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{07E9C1F5-6973-C4E7-F22A-8FC08C2AB984}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07E9C1F5-6973-C4E7-F22A-8FC08C2AB984}"/>
             </a:ext>
             <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" pred="{DD5544AB-9FFC-142D-6E26-CD35F994ABBA}"/>
+              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{DD5544AB-9FFC-142D-6E26-CD35F994ABBA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6356,10 +6356,10 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6715A6CC-3A6A-A1DB-3E76-6B956BB6C7D0}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6715A6CC-3A6A-A1DB-3E76-6B956BB6C7D0}"/>
             </a:ext>
             <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" pred="{07E9C1F5-6973-C4E7-F22A-8FC08C2AB984}"/>
+              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{07E9C1F5-6973-C4E7-F22A-8FC08C2AB984}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6435,10 +6435,10 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{67A41256-9299-4DF9-9708-1493DA40FCED}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67A41256-9299-4DF9-9708-1493DA40FCED}"/>
             </a:ext>
             <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" pred="{6715A6CC-3A6A-A1DB-3E76-6B956BB6C7D0}"/>
+              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{6715A6CC-3A6A-A1DB-3E76-6B956BB6C7D0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6608,10 +6608,10 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8AA0A94E-7223-4757-BA7D-46C6CDA719B2}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8AA0A94E-7223-4757-BA7D-46C6CDA719B2}"/>
             </a:ext>
             <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" pred="{67A41256-9299-4DF9-9708-1493DA40FCED}"/>
+              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{67A41256-9299-4DF9-9708-1493DA40FCED}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7018,10 +7018,10 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8AA0A94E-7223-4757-BA7D-46C6CDA719B2}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8AA0A94E-7223-4757-BA7D-46C6CDA719B2}"/>
             </a:ext>
             <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" pred="{67A41256-9299-4DF9-9708-1493DA40FCED}"/>
+              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{67A41256-9299-4DF9-9708-1493DA40FCED}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7197,10 +7197,10 @@
         <xdr:cNvPr id="2" name="Imagem 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{DD5544AB-9FFC-142D-6E26-CD35F994ABBA}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD5544AB-9FFC-142D-6E26-CD35F994ABBA}"/>
             </a:ext>
             <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" pred="{07E9C1F5-6973-C4E7-F22A-8FC08C2AB984}"/>
+              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{07E9C1F5-6973-C4E7-F22A-8FC08C2AB984}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7244,10 +7244,10 @@
         <xdr:cNvPr id="3" name="Retângulo 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{07E9C1F5-6973-C4E7-F22A-8FC08C2AB984}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07E9C1F5-6973-C4E7-F22A-8FC08C2AB984}"/>
             </a:ext>
             <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" pred="{DD5544AB-9FFC-142D-6E26-CD35F994ABBA}"/>
+              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{DD5544AB-9FFC-142D-6E26-CD35F994ABBA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7322,10 +7322,10 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6715A6CC-3A6A-A1DB-3E76-6B956BB6C7D0}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6715A6CC-3A6A-A1DB-3E76-6B956BB6C7D0}"/>
             </a:ext>
             <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" pred="{07E9C1F5-6973-C4E7-F22A-8FC08C2AB984}"/>
+              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{07E9C1F5-6973-C4E7-F22A-8FC08C2AB984}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7401,10 +7401,10 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{67A41256-9299-4DF9-9708-1493DA40FCED}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67A41256-9299-4DF9-9708-1493DA40FCED}"/>
             </a:ext>
             <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" pred="{6715A6CC-3A6A-A1DB-3E76-6B956BB6C7D0}"/>
+              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{6715A6CC-3A6A-A1DB-3E76-6B956BB6C7D0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7574,10 +7574,10 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8AA0A94E-7223-4757-BA7D-46C6CDA719B2}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8AA0A94E-7223-4757-BA7D-46C6CDA719B2}"/>
             </a:ext>
             <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" pred="{67A41256-9299-4DF9-9708-1493DA40FCED}"/>
+              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{67A41256-9299-4DF9-9708-1493DA40FCED}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8198,6 +8198,7 @@
               <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
               <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
+            <a:pPr algn="ctr"/>
             <a:t>R$ 13.000,00</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="2000" b="1" i="0" u="none" strike="noStrike">
@@ -8302,10 +8303,10 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8AA0A94E-7223-4757-BA7D-46C6CDA719B2}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8AA0A94E-7223-4757-BA7D-46C6CDA719B2}"/>
             </a:ext>
             <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" pred="{67A41256-9299-4DF9-9708-1493DA40FCED}"/>
+              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{67A41256-9299-4DF9-9708-1493DA40FCED}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8465,44 +8466,44 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TITULAR" displayName="TITULAR" ref="C6:D19" headerRowCount="0" totalsRowShown="0" headerRowDxfId="36" tableBorderDxfId="35" totalsRowBorderDxfId="34">
   <tableColumns count="2">
     <tableColumn id="1" name="Colunas1" headerRowDxfId="33" dataDxfId="32"/>
-    <tableColumn id="2" name="Colunas2" headerRowDxfId="31" dataDxfId="10" headerRowCellStyle="Entrada" dataCellStyle="Entrada"/>
+    <tableColumn id="2" name="Colunas2" headerRowDxfId="31" dataDxfId="30" headerRowCellStyle="Entrada" dataCellStyle="Entrada"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TITULAR3" displayName="TITULAR3" ref="C10:D12" headerRowCount="0" totalsRowShown="0" headerRowDxfId="30" tableBorderDxfId="29" totalsRowBorderDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TITULAR3" displayName="TITULAR3" ref="C10:D12" headerRowCount="0" totalsRowShown="0" headerRowDxfId="29" tableBorderDxfId="28" totalsRowBorderDxfId="27">
   <tableColumns count="2">
     <tableColumn id="1" name="Colunas1" headerRowDxfId="26" dataDxfId="25"/>
-    <tableColumn id="2" name="Colunas2" headerRowDxfId="27" dataDxfId="9" headerRowCellStyle="Entrada" dataCellStyle="Entrada"/>
+    <tableColumn id="2" name="Colunas2" headerRowDxfId="24" dataDxfId="23" headerRowCellStyle="Entrada" dataCellStyle="Entrada"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="TITULAR35" displayName="TITULAR35" ref="C16:D18" headerRowCount="0" totalsRowShown="0" headerRowDxfId="24" tableBorderDxfId="23" totalsRowBorderDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="TITULAR35" displayName="TITULAR35" ref="C16:D18" headerRowCount="0" totalsRowShown="0" headerRowDxfId="22" tableBorderDxfId="21" totalsRowBorderDxfId="20">
   <tableColumns count="2">
-    <tableColumn id="1" name="Colunas1" headerRowDxfId="21" dataDxfId="20"/>
-    <tableColumn id="2" name="Colunas2" headerRowDxfId="19" dataDxfId="8" headerRowCellStyle="Entrada" dataCellStyle="Entrada"/>
+    <tableColumn id="1" name="Colunas1" headerRowDxfId="19" dataDxfId="18"/>
+    <tableColumn id="2" name="Colunas2" headerRowDxfId="17" dataDxfId="16" headerRowCellStyle="Entrada" dataCellStyle="Entrada"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="TITULAR36" displayName="TITULAR36" ref="C22:D24" headerRowCount="0" totalsRowShown="0" headerRowDxfId="18" tableBorderDxfId="17" totalsRowBorderDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="TITULAR36" displayName="TITULAR36" ref="C22:D24" headerRowCount="0" totalsRowShown="0" headerRowDxfId="15" tableBorderDxfId="14" totalsRowBorderDxfId="13">
   <tableColumns count="2">
-    <tableColumn id="1" name="Colunas1" headerRowDxfId="15" dataDxfId="14"/>
-    <tableColumn id="2" name="Colunas2" headerRowDxfId="13" dataDxfId="7" headerRowCellStyle="Entrada" dataCellStyle="Entrada"/>
+    <tableColumn id="1" name="Colunas1" headerRowDxfId="12" dataDxfId="11"/>
+    <tableColumn id="2" name="Colunas2" headerRowDxfId="10" dataDxfId="9" headerRowCellStyle="Entrada" dataCellStyle="Entrada"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="tabela_banco" displayName="tabela_banco" ref="A1:A51" totalsRowShown="0" headerRowDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="tabela_banco" displayName="tabela_banco" ref="A1:A51" totalsRowShown="0" headerRowDxfId="8">
   <autoFilter ref="A1:A51"/>
   <tableColumns count="1">
     <tableColumn id="1" name="bancos"/>
@@ -8512,12 +8513,12 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="TABELA_ENTRADAS" displayName="TABELA_ENTRADAS" ref="C8:E35" totalsRowCount="1" headerRowDxfId="11" dataDxfId="3">
-  <autoFilter ref="C8:E35"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="TABELA_ENTRADAS" displayName="TABELA_ENTRADAS" ref="C8:E35" totalsRowCount="1" headerRowDxfId="7" dataDxfId="6">
+  <autoFilter ref="C8:E34"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="DATA" dataDxfId="6" totalsRowDxfId="2"/>
-    <tableColumn id="2" name="CATEGORIA" dataDxfId="5" totalsRowDxfId="1"/>
-    <tableColumn id="3" name="VALOR" totalsRowFunction="sum" dataDxfId="4" totalsRowDxfId="0" dataCellStyle="Moeda"/>
+    <tableColumn id="1" name="DATA" dataDxfId="5" totalsRowDxfId="2"/>
+    <tableColumn id="2" name="CATEGORIA" dataDxfId="4" totalsRowDxfId="1"/>
+    <tableColumn id="3" name="VALOR" totalsRowFunction="sum" dataDxfId="3" totalsRowDxfId="0" dataCellStyle="Moeda"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8878,16 +8879,16 @@
       <c r="D3" s="16"/>
     </row>
     <row r="4" spans="3:4" ht="15.75" customHeight="1" thickTop="1">
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="20"/>
+      <c r="D4" s="43"/>
     </row>
     <row r="6" spans="3:4" ht="15.75">
       <c r="C6" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="25" t="s">
         <v>21</v>
       </c>
     </row>
@@ -8895,7 +8896,7 @@
       <c r="C7" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="26">
         <v>12456310039</v>
       </c>
     </row>
@@ -8903,7 +8904,7 @@
       <c r="C8" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="32">
+      <c r="D8" s="27">
         <v>35453</v>
       </c>
     </row>
@@ -8911,7 +8912,7 @@
       <c r="C9" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="33">
+      <c r="D9" s="28">
         <v>5564312</v>
       </c>
     </row>
@@ -8919,7 +8920,7 @@
       <c r="C10" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="33" t="s">
+      <c r="D10" s="28" t="s">
         <v>22</v>
       </c>
     </row>
@@ -8927,7 +8928,7 @@
       <c r="C11" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="33" t="s">
+      <c r="D11" s="28" t="s">
         <v>23</v>
       </c>
     </row>
@@ -8935,7 +8936,7 @@
       <c r="C12" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="33" t="s">
+      <c r="D12" s="28" t="s">
         <v>24</v>
       </c>
     </row>
@@ -8943,7 +8944,7 @@
       <c r="C13" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="34">
+      <c r="D13" s="29">
         <v>870000430</v>
       </c>
     </row>
@@ -8951,7 +8952,7 @@
       <c r="C14" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="35">
+      <c r="D14" s="30">
         <v>41999453820</v>
       </c>
     </row>
@@ -8959,7 +8960,7 @@
       <c r="C15" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="35">
+      <c r="D15" s="30">
         <v>41988256314</v>
       </c>
     </row>
@@ -8967,7 +8968,7 @@
       <c r="C16" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D16" s="36" t="s">
+      <c r="D16" s="31" t="s">
         <v>25</v>
       </c>
     </row>
@@ -8975,7 +8976,7 @@
       <c r="C17" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D17" s="33" t="s">
+      <c r="D17" s="28" t="s">
         <v>26</v>
       </c>
     </row>
@@ -8983,7 +8984,7 @@
       <c r="C18" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D18" s="33" t="s">
+      <c r="D18" s="28" t="s">
         <v>26</v>
       </c>
     </row>
@@ -8991,21 +8992,21 @@
       <c r="C19" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="37" t="s">
+      <c r="D19" s="32" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="C20" s="21"/>
-      <c r="D20" s="21"/>
+      <c r="C20" s="44"/>
+      <c r="D20" s="44"/>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="44" t="s">
+      <c r="A21" s="39" t="s">
         <v>96</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="2">
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C20:D20"/>
@@ -9044,34 +9045,34 @@
       <c r="D3" s="16"/>
     </row>
     <row r="4" spans="2:9" ht="15.75" thickTop="1">
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="20"/>
+      <c r="D4" s="43"/>
     </row>
     <row r="6" spans="2:9" ht="17.25" customHeight="1">
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="21" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="17.25" customHeight="1">
-      <c r="C7" s="26">
+      <c r="C7" s="45">
         <f>D11+D17+D23</f>
         <v>2295283.4500000002</v>
       </c>
-      <c r="D7" s="27"/>
+      <c r="D7" s="46"/>
     </row>
     <row r="9" spans="2:9">
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="22"/>
+      <c r="D9" s="20"/>
     </row>
     <row r="10" spans="2:9" ht="15.75">
       <c r="C10" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="38" t="s">
+      <c r="D10" s="33" t="s">
         <v>40</v>
       </c>
     </row>
@@ -9079,7 +9080,7 @@
       <c r="C11" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="39">
+      <c r="D11" s="34">
         <v>500000</v>
       </c>
     </row>
@@ -9087,7 +9088,7 @@
       <c r="C12" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="40" t="s">
+      <c r="D12" s="35" t="s">
         <v>36</v>
       </c>
     </row>
@@ -9101,10 +9102,10 @@
     </row>
     <row r="15" spans="2:9">
       <c r="B15" s="11"/>
-      <c r="C15" s="22" t="s">
+      <c r="C15" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="22"/>
+      <c r="D15" s="20"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="11"/>
@@ -9116,7 +9117,7 @@
       <c r="C16" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="D16" s="38" t="s">
+      <c r="D16" s="33" t="s">
         <v>64</v>
       </c>
       <c r="E16" s="11"/>
@@ -9130,7 +9131,7 @@
       <c r="C17" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="D17" s="39">
+      <c r="D17" s="34">
         <v>1560635.23</v>
       </c>
       <c r="E17" s="11"/>
@@ -9144,7 +9145,7 @@
       <c r="C18" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="D18" s="40" t="s">
+      <c r="D18" s="35" t="s">
         <v>36</v>
       </c>
       <c r="E18" s="11"/>
@@ -9174,14 +9175,14 @@
       <c r="I20" s="11"/>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="44" t="s">
+      <c r="A21" s="39" t="s">
         <v>96</v>
       </c>
       <c r="B21" s="11"/>
-      <c r="C21" s="22" t="s">
+      <c r="C21" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="22"/>
+      <c r="D21" s="20"/>
       <c r="E21" s="11"/>
       <c r="F21" s="11"/>
       <c r="G21" s="11"/>
@@ -9193,7 +9194,7 @@
       <c r="C22" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="D22" s="38" t="s">
+      <c r="D22" s="33" t="s">
         <v>45</v>
       </c>
       <c r="E22" s="11"/>
@@ -9207,7 +9208,7 @@
       <c r="C23" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="D23" s="39">
+      <c r="D23" s="34">
         <v>234648.22</v>
       </c>
       <c r="E23" s="11"/>
@@ -9221,7 +9222,7 @@
       <c r="C24" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="D24" s="40" t="s">
+      <c r="D24" s="35" t="s">
         <v>36</v>
       </c>
       <c r="E24" s="11"/>
@@ -9303,7 +9304,7 @@
       <c r="I33" s="11"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="2">
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C7:D7"/>
@@ -9340,7 +9341,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="23" t="s">
         <v>37</v>
       </c>
     </row>
@@ -9621,190 +9622,190 @@
       <c r="D3" s="16"/>
     </row>
     <row r="4" spans="3:5" ht="15.75" thickTop="1">
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="43" t="s">
         <v>89</v>
       </c>
-      <c r="D4" s="20"/>
+      <c r="D4" s="43"/>
     </row>
     <row r="7" spans="3:5">
-      <c r="C7" s="28" t="s">
+      <c r="C7" s="47" t="s">
         <v>93</v>
       </c>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
+      <c r="D7" s="47"/>
+      <c r="E7" s="47"/>
     </row>
     <row r="8" spans="3:5">
-      <c r="C8" s="29" t="s">
+      <c r="C8" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="D8" s="29" t="s">
+      <c r="D8" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="E8" s="29" t="s">
+      <c r="E8" s="24" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="9" spans="3:5">
-      <c r="C9" s="41">
+      <c r="C9" s="36">
         <v>46296</v>
       </c>
-      <c r="D9" s="42" t="s">
+      <c r="D9" s="37" t="s">
         <v>95</v>
       </c>
-      <c r="E9" s="43">
+      <c r="E9" s="38">
         <v>2500</v>
       </c>
     </row>
     <row r="10" spans="3:5">
-      <c r="C10" s="41">
+      <c r="C10" s="36">
         <v>46300</v>
       </c>
-      <c r="D10" s="42" t="s">
+      <c r="D10" s="37" t="s">
         <v>97</v>
       </c>
-      <c r="E10" s="43">
+      <c r="E10" s="38">
         <v>4000</v>
       </c>
     </row>
     <row r="11" spans="3:5">
-      <c r="C11" s="41">
+      <c r="C11" s="36">
         <v>46304</v>
       </c>
-      <c r="D11" s="42" t="s">
+      <c r="D11" s="37" t="s">
         <v>94</v>
       </c>
-      <c r="E11" s="43">
+      <c r="E11" s="38">
         <v>6500</v>
       </c>
     </row>
     <row r="12" spans="3:5">
-      <c r="C12" s="41"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="43"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="37"/>
+      <c r="E12" s="38"/>
     </row>
     <row r="13" spans="3:5">
-      <c r="C13" s="41"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="43"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="37"/>
+      <c r="E13" s="38"/>
     </row>
     <row r="14" spans="3:5">
-      <c r="C14" s="41"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="43"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="37"/>
+      <c r="E14" s="38"/>
     </row>
     <row r="15" spans="3:5">
-      <c r="C15" s="41"/>
-      <c r="D15" s="42"/>
-      <c r="E15" s="43"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="37"/>
+      <c r="E15" s="38"/>
     </row>
     <row r="16" spans="3:5">
-      <c r="C16" s="41"/>
-      <c r="D16" s="42"/>
-      <c r="E16" s="43"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="37"/>
+      <c r="E16" s="38"/>
     </row>
     <row r="17" spans="1:5">
-      <c r="C17" s="41"/>
-      <c r="D17" s="42"/>
-      <c r="E17" s="43"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="37"/>
+      <c r="E17" s="38"/>
     </row>
     <row r="18" spans="1:5">
-      <c r="C18" s="41"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="43"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="37"/>
+      <c r="E18" s="38"/>
     </row>
     <row r="19" spans="1:5">
-      <c r="C19" s="41"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="43"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="37"/>
+      <c r="E19" s="38"/>
     </row>
     <row r="20" spans="1:5">
-      <c r="C20" s="41"/>
-      <c r="D20" s="42"/>
-      <c r="E20" s="43"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="37"/>
+      <c r="E20" s="38"/>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="44" t="s">
+      <c r="A21" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="C21" s="41"/>
-      <c r="D21" s="42"/>
-      <c r="E21" s="43"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="38"/>
     </row>
     <row r="22" spans="1:5">
-      <c r="C22" s="41"/>
-      <c r="D22" s="42"/>
-      <c r="E22" s="43"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="37"/>
+      <c r="E22" s="38"/>
     </row>
     <row r="23" spans="1:5">
-      <c r="C23" s="41"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="43"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="38"/>
     </row>
     <row r="24" spans="1:5">
-      <c r="C24" s="41"/>
-      <c r="D24" s="42"/>
-      <c r="E24" s="43"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="37"/>
+      <c r="E24" s="38"/>
     </row>
     <row r="25" spans="1:5">
-      <c r="C25" s="41"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="43"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="38"/>
     </row>
     <row r="26" spans="1:5">
-      <c r="C26" s="41"/>
-      <c r="D26" s="42"/>
-      <c r="E26" s="43"/>
+      <c r="C26" s="36"/>
+      <c r="D26" s="37"/>
+      <c r="E26" s="38"/>
     </row>
     <row r="27" spans="1:5">
-      <c r="C27" s="41"/>
-      <c r="D27" s="42"/>
-      <c r="E27" s="43"/>
+      <c r="C27" s="36"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="38"/>
     </row>
     <row r="28" spans="1:5">
-      <c r="C28" s="41"/>
-      <c r="D28" s="42"/>
-      <c r="E28" s="43"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="37"/>
+      <c r="E28" s="38"/>
     </row>
     <row r="29" spans="1:5">
-      <c r="C29" s="41"/>
-      <c r="D29" s="42"/>
-      <c r="E29" s="43"/>
+      <c r="C29" s="36"/>
+      <c r="D29" s="37"/>
+      <c r="E29" s="38"/>
     </row>
     <row r="30" spans="1:5">
-      <c r="C30" s="41"/>
-      <c r="D30" s="42"/>
-      <c r="E30" s="43"/>
+      <c r="C30" s="36"/>
+      <c r="D30" s="37"/>
+      <c r="E30" s="38"/>
     </row>
     <row r="31" spans="1:5">
-      <c r="C31" s="41"/>
-      <c r="D31" s="42"/>
-      <c r="E31" s="43"/>
+      <c r="C31" s="36"/>
+      <c r="D31" s="37"/>
+      <c r="E31" s="38"/>
     </row>
     <row r="32" spans="1:5">
-      <c r="C32" s="41"/>
-      <c r="D32" s="42"/>
-      <c r="E32" s="43"/>
+      <c r="C32" s="36"/>
+      <c r="D32" s="37"/>
+      <c r="E32" s="38"/>
     </row>
     <row r="33" spans="3:5">
-      <c r="C33" s="41"/>
-      <c r="D33" s="42"/>
-      <c r="E33" s="43"/>
+      <c r="C33" s="36"/>
+      <c r="D33" s="37"/>
+      <c r="E33" s="38"/>
     </row>
     <row r="34" spans="3:5">
-      <c r="C34" s="41"/>
-      <c r="D34" s="42"/>
-      <c r="E34" s="43"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="37"/>
+      <c r="E34" s="38"/>
     </row>
     <row r="35" spans="3:5">
-      <c r="C35" s="42"/>
-      <c r="D35" s="42"/>
-      <c r="E35" s="43">
+      <c r="C35" s="37"/>
+      <c r="D35" s="37"/>
+      <c r="E35" s="38">
         <f>SUBTOTAL(109,TABELA_ENTRADAS[VALOR])</f>
         <v>13000</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="2">
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C7:E7"/>
@@ -9835,20 +9836,21 @@
   </cols>
   <sheetData>
     <row r="16" spans="16:16">
-      <c r="P16" s="47">
+      <c r="P16" s="42">
         <f>TABELA_ENTRADAS[[#Totals],[VALOR]]</f>
         <v>13000</v>
       </c>
     </row>
     <row r="18" spans="1:15">
-      <c r="O18" s="46"/>
+      <c r="O18" s="41"/>
     </row>
     <row r="21" spans="1:15">
-      <c r="A21" s="44" t="s">
+      <c r="A21" s="39" t="s">
         <v>96</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -9872,31 +9874,31 @@
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="24" t="str">
+      <c r="A2" s="22" t="str">
         <f>INFORMES!D10</f>
         <v>104 - Caixa Econômica Federal</v>
       </c>
-      <c r="B2" s="45">
+      <c r="B2" s="40">
         <f>INFORMES!D11</f>
         <v>500000</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="24" t="str">
+      <c r="A3" s="22" t="str">
         <f>INFORMES!D16</f>
         <v>422 - Banco Safra</v>
       </c>
-      <c r="B3" s="45">
+      <c r="B3" s="40">
         <f>INFORMES!D17</f>
         <v>1560635.23</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="24" t="str">
+      <c r="A4" s="22" t="str">
         <f>INFORMES!D22</f>
         <v>212 - Banco Original</v>
       </c>
-      <c r="B4" s="45">
+      <c r="B4" s="40">
         <f>INFORMES!D23</f>
         <v>234648.22</v>
       </c>
